--- a/inputData/inputData.xlsx
+++ b/inputData/inputData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/inputData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48D1582E-D27E-2F41-B1C0-048748198FFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09258F7E-AE3E-0F42-8159-2876CA79017F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16340" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16340" activeTab="2" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="PlaneData" sheetId="7" r:id="rId1"/>
@@ -670,7 +670,7 @@
         <v>3</v>
       </c>
       <c r="D1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="D2">
         <f ca="1">RANDBETWEEN(10,120)</f>
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -1674,11 +1674,11 @@
       </c>
       <c r="I2">
         <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K2">
         <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L2">
         <f ca="1">RANDBETWEEN(1,5)</f>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="D3">
         <f t="shared" ref="D3:D21" ca="1" si="0">RANDBETWEEN(10,120)</f>
-        <v>70</v>
+        <v>106</v>
       </c>
       <c r="E3">
         <v>3</v>
@@ -1711,11 +1711,11 @@
       </c>
       <c r="K3">
         <f t="shared" ref="K3:L21" ca="1" si="2">RANDBETWEEN(1,5)</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L3">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="D4">
         <f t="shared" ca="1" si="0"/>
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="D5">
         <f t="shared" ca="1" si="0"/>
-        <v>64</v>
+        <v>110</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I5">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K5">
         <f t="shared" ca="1" si="2"/>
@@ -1781,7 +1781,7 @@
       </c>
       <c r="L5">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="D6">
         <f t="shared" ca="1" si="0"/>
-        <v>116</v>
+        <v>17</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1806,11 +1806,11 @@
       </c>
       <c r="I6">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K6">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L6">
         <f t="shared" ca="1" si="2"/>
@@ -1829,7 +1829,7 @@
       </c>
       <c r="D7">
         <f t="shared" ca="1" si="0"/>
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -1839,15 +1839,15 @@
       </c>
       <c r="I7">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K7">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L7">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="D8">
         <f t="shared" ca="1" si="0"/>
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -1876,11 +1876,11 @@
       </c>
       <c r="K8">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L8">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="D9">
         <f t="shared" ca="1" si="0"/>
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="E9">
         <v>2</v>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="I9">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K9">
         <f t="shared" ca="1" si="2"/>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="L9">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="D10">
         <f t="shared" ca="1" si="0"/>
-        <v>81</v>
+        <v>16</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -1938,7 +1938,7 @@
       </c>
       <c r="I10">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K10">
         <f t="shared" ca="1" si="2"/>
@@ -1946,7 +1946,7 @@
       </c>
       <c r="L10">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="D11">
         <f t="shared" ca="1" si="0"/>
-        <v>65</v>
+        <v>111</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -1971,15 +1971,15 @@
       </c>
       <c r="I11">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K11">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L11">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="D12">
         <f t="shared" ca="1" si="0"/>
-        <v>61</v>
+        <v>21</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="I12">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K12">
         <f t="shared" ca="1" si="2"/>
@@ -2012,7 +2012,7 @@
       </c>
       <c r="L12">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="D13">
         <f t="shared" ca="1" si="0"/>
-        <v>83</v>
+        <v>36</v>
       </c>
       <c r="E13">
         <v>2</v>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="I13">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K13">
         <f t="shared" ca="1" si="2"/>
@@ -2045,7 +2045,7 @@
       </c>
       <c r="L13">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -2060,7 +2060,7 @@
       </c>
       <c r="D14">
         <f t="shared" ca="1" si="0"/>
-        <v>115</v>
+        <v>40</v>
       </c>
       <c r="E14">
         <v>2</v>
@@ -2070,15 +2070,15 @@
       </c>
       <c r="I14">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K14">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L14">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="D15">
         <f t="shared" ca="1" si="0"/>
-        <v>33</v>
+        <v>89</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -2103,15 +2103,15 @@
       </c>
       <c r="I15">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K15">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L15">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="D16">
         <f t="shared" ca="1" si="0"/>
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E16">
         <v>3</v>
@@ -2136,15 +2136,15 @@
       </c>
       <c r="I16">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K16">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L16">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:24">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="D17">
         <f t="shared" ca="1" si="0"/>
-        <v>88</v>
+        <v>40</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="I17">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K17">
         <f t="shared" ca="1" si="2"/>
@@ -2177,7 +2177,7 @@
       </c>
       <c r="L17">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:24">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="D18">
         <f t="shared" ca="1" si="0"/>
-        <v>112</v>
+        <v>35</v>
       </c>
       <c r="E18">
         <v>2</v>
@@ -2202,15 +2202,15 @@
       </c>
       <c r="I18">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K18">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L18">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:24">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="D19">
         <f t="shared" ca="1" si="0"/>
-        <v>98</v>
+        <v>34</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -2235,7 +2235,7 @@
       </c>
       <c r="I19">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K19">
         <f t="shared" ca="1" si="2"/>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="L19">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:24">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="D20">
         <f t="shared" ca="1" si="0"/>
-        <v>18</v>
+        <v>72</v>
       </c>
       <c r="E20">
         <v>2</v>
@@ -2268,15 +2268,15 @@
       </c>
       <c r="I20">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K20">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L20">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:24">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="D21">
         <f t="shared" ca="1" si="0"/>
-        <v>14</v>
+        <v>90</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -2301,11 +2301,11 @@
       </c>
       <c r="I21">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K21">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L21">
         <f t="shared" ca="1" si="2"/>

--- a/inputData/inputData.xlsx
+++ b/inputData/inputData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/inputData/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kapta\Documents\DTU\Speciale\GitHubFiles\inputData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48D1582E-D27E-2F41-B1C0-048748198FFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB02FBFD-7CAE-452B-90DF-6CB665492C2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16340" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="PlaneData" sheetId="7" r:id="rId1"/>
@@ -545,7 +545,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A94FE46B-0EE8-4D7E-956E-06AD6DDE4FF5}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
@@ -598,7 +598,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{332D5C3C-A1DF-48A5-A3F8-29AFDB8C103D}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -607,7 +607,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64A48C4B-C23A-0343-9CD4-B20C0FE9227B}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
@@ -652,7 +652,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3245F359-CA05-2247-86C6-92433A84B0A2}">
   <dimension ref="A1:F20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col min="3" max="3" width="22.5" customWidth="1"/>
     <col min="4" max="4" width="13.33203125" bestFit="1" customWidth="1"/>
@@ -670,7 +670,7 @@
         <v>3</v>
       </c>
       <c r="D1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -773,7 +773,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0891C305-141D-384C-BB9E-30507F3FCDCC}">
   <dimension ref="A1:X32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col min="5" max="5" width="11.83203125" customWidth="1"/>
     <col min="6" max="6" width="11.5" customWidth="1"/>
@@ -1341,7 +1341,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF01B7F4-A8F2-E74F-93E1-1ACB4B99B891}">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
@@ -1411,7 +1411,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4154E97-9715-C248-8300-688A466787B4}">
   <dimension ref="A1:K6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col min="3" max="3" width="12.5" customWidth="1"/>
   </cols>
@@ -1490,7 +1490,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30A04F2A-161E-4502-9547-1DD0A31CBA64}">
   <dimension ref="A1:G6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col min="3" max="3" width="12.5" customWidth="1"/>
     <col min="4" max="4" width="17.5" bestFit="1" customWidth="1"/>
@@ -1623,7 +1623,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A73ABDEA-DD83-4C31-B1A2-B93032C8B1F1}">
   <dimension ref="A1:X32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col min="5" max="5" width="11.83203125" customWidth="1"/>
     <col min="6" max="6" width="11.5" customWidth="1"/>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="D2">
         <f ca="1">RANDBETWEEN(10,120)</f>
-        <v>31</v>
+        <v>114</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -1674,15 +1674,15 @@
       </c>
       <c r="I2">
         <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K2">
         <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L2">
         <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="D3">
         <f t="shared" ref="D3:D21" ca="1" si="0">RANDBETWEEN(10,120)</f>
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E3">
         <v>3</v>
@@ -1707,11 +1707,11 @@
       </c>
       <c r="I3">
         <f t="shared" ref="I3:I21" ca="1" si="1">RANDBETWEEN(1,5)</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K3">
         <f t="shared" ref="K3:L21" ca="1" si="2">RANDBETWEEN(1,5)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L3">
         <f t="shared" ca="1" si="2"/>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="D4">
         <f t="shared" ca="1" si="0"/>
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -1740,15 +1740,15 @@
       </c>
       <c r="I4">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K4">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L4">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="D5">
         <f t="shared" ca="1" si="0"/>
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -1773,11 +1773,11 @@
       </c>
       <c r="I5">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K5">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L5">
         <f t="shared" ca="1" si="2"/>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="D6">
         <f t="shared" ca="1" si="0"/>
-        <v>116</v>
+        <v>76</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1806,15 +1806,15 @@
       </c>
       <c r="I6">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K6">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L6">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="D7">
         <f t="shared" ca="1" si="0"/>
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="I7">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K7">
         <f t="shared" ca="1" si="2"/>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="L7">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="D8">
         <f t="shared" ca="1" si="0"/>
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="K8">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L8">
         <f t="shared" ca="1" si="2"/>
@@ -1895,7 +1895,7 @@
       </c>
       <c r="D9">
         <f t="shared" ca="1" si="0"/>
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="E9">
         <v>2</v>
@@ -1909,11 +1909,11 @@
       </c>
       <c r="K9">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L9">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="D10">
         <f t="shared" ca="1" si="0"/>
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -1942,11 +1942,11 @@
       </c>
       <c r="K10">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L10">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="D11">
         <f t="shared" ca="1" si="0"/>
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -1971,15 +1971,15 @@
       </c>
       <c r="I11">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K11">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L11">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="D12">
         <f t="shared" ca="1" si="0"/>
-        <v>61</v>
+        <v>117</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="K12">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L12">
         <f t="shared" ca="1" si="2"/>
@@ -2027,7 +2027,7 @@
       </c>
       <c r="D13">
         <f t="shared" ca="1" si="0"/>
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="E13">
         <v>2</v>
@@ -2037,15 +2037,15 @@
       </c>
       <c r="I13">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K13">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L13">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -2060,7 +2060,7 @@
       </c>
       <c r="D14">
         <f t="shared" ca="1" si="0"/>
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E14">
         <v>2</v>
@@ -2070,15 +2070,15 @@
       </c>
       <c r="I14">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K14">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L14">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="D15">
         <f t="shared" ca="1" si="0"/>
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="I15">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K15">
         <f t="shared" ca="1" si="2"/>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="L15">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="D16">
         <f t="shared" ca="1" si="0"/>
-        <v>15</v>
+        <v>80</v>
       </c>
       <c r="E16">
         <v>3</v>
@@ -2136,15 +2136,15 @@
       </c>
       <c r="I16">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K16">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L16">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:24">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="D17">
         <f t="shared" ca="1" si="0"/>
-        <v>88</v>
+        <v>118</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -2169,15 +2169,15 @@
       </c>
       <c r="I17">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K17">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L17">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:24">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="D18">
         <f t="shared" ca="1" si="0"/>
-        <v>112</v>
+        <v>50</v>
       </c>
       <c r="E18">
         <v>2</v>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="I18">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K18">
         <f t="shared" ca="1" si="2"/>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="L18">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:24">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="D19">
         <f t="shared" ca="1" si="0"/>
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -2235,15 +2235,15 @@
       </c>
       <c r="I19">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K19">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L19">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:24">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="D20">
         <f t="shared" ca="1" si="0"/>
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="E20">
         <v>2</v>
@@ -2268,15 +2268,15 @@
       </c>
       <c r="I20">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K20">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L20">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:24">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="D21">
         <f t="shared" ca="1" si="0"/>
-        <v>14</v>
+        <v>72</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -2305,11 +2305,11 @@
       </c>
       <c r="K21">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L21">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:24">
@@ -2454,7 +2454,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E3CF6DF-5DC6-4F82-AD2C-07BC625FD2D9}">
   <dimension ref="A1:G8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col min="5" max="5" width="19.6640625" bestFit="1" customWidth="1"/>
   </cols>

--- a/inputData/inputData.xlsx
+++ b/inputData/inputData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/inputData/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kapta\Documents\DTU\Speciale\GitHubFiles\inputData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09258F7E-AE3E-0F42-8159-2876CA79017F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB02FBFD-7CAE-452B-90DF-6CB665492C2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16340" activeTab="2" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="PlaneData" sheetId="7" r:id="rId1"/>
@@ -545,7 +545,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A94FE46B-0EE8-4D7E-956E-06AD6DDE4FF5}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
@@ -598,7 +598,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{332D5C3C-A1DF-48A5-A3F8-29AFDB8C103D}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -607,7 +607,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64A48C4B-C23A-0343-9CD4-B20C0FE9227B}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
@@ -652,7 +652,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3245F359-CA05-2247-86C6-92433A84B0A2}">
   <dimension ref="A1:F20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col min="3" max="3" width="22.5" customWidth="1"/>
     <col min="4" max="4" width="13.33203125" bestFit="1" customWidth="1"/>
@@ -773,7 +773,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0891C305-141D-384C-BB9E-30507F3FCDCC}">
   <dimension ref="A1:X32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col min="5" max="5" width="11.83203125" customWidth="1"/>
     <col min="6" max="6" width="11.5" customWidth="1"/>
@@ -1341,7 +1341,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF01B7F4-A8F2-E74F-93E1-1ACB4B99B891}">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
@@ -1411,7 +1411,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4154E97-9715-C248-8300-688A466787B4}">
   <dimension ref="A1:K6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col min="3" max="3" width="12.5" customWidth="1"/>
   </cols>
@@ -1490,7 +1490,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30A04F2A-161E-4502-9547-1DD0A31CBA64}">
   <dimension ref="A1:G6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col min="3" max="3" width="12.5" customWidth="1"/>
     <col min="4" max="4" width="17.5" bestFit="1" customWidth="1"/>
@@ -1623,7 +1623,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A73ABDEA-DD83-4C31-B1A2-B93032C8B1F1}">
   <dimension ref="A1:X32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col min="5" max="5" width="11.83203125" customWidth="1"/>
     <col min="6" max="6" width="11.5" customWidth="1"/>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="D2">
         <f ca="1">RANDBETWEEN(10,120)</f>
-        <v>20</v>
+        <v>114</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="I2">
         <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K2">
         <f ca="1">RANDBETWEEN(1,5)</f>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L2">
         <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="D3">
         <f t="shared" ref="D3:D21" ca="1" si="0">RANDBETWEEN(10,120)</f>
-        <v>106</v>
+        <v>72</v>
       </c>
       <c r="E3">
         <v>3</v>
@@ -1707,15 +1707,15 @@
       </c>
       <c r="I3">
         <f t="shared" ref="I3:I21" ca="1" si="1">RANDBETWEEN(1,5)</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K3">
         <f t="shared" ref="K3:L21" ca="1" si="2">RANDBETWEEN(1,5)</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L3">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="D4">
         <f t="shared" ca="1" si="0"/>
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -1740,15 +1740,15 @@
       </c>
       <c r="I4">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K4">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L4">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="D5">
         <f t="shared" ca="1" si="0"/>
-        <v>110</v>
+        <v>72</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -1773,15 +1773,15 @@
       </c>
       <c r="I5">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K5">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L5">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="D6">
         <f t="shared" ca="1" si="0"/>
-        <v>17</v>
+        <v>76</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1806,15 +1806,15 @@
       </c>
       <c r="I6">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K6">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L6">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="D7">
         <f t="shared" ca="1" si="0"/>
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -1839,11 +1839,11 @@
       </c>
       <c r="I7">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K7">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L7">
         <f t="shared" ca="1" si="2"/>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="D8">
         <f t="shared" ca="1" si="0"/>
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="L8">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="D9">
         <f t="shared" ca="1" si="0"/>
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="E9">
         <v>2</v>
@@ -1905,15 +1905,15 @@
       </c>
       <c r="I9">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K9">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L9">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="D10">
         <f t="shared" ca="1" si="0"/>
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -1938,15 +1938,15 @@
       </c>
       <c r="I10">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K10">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L10">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="D11">
         <f t="shared" ca="1" si="0"/>
-        <v>111</v>
+        <v>62</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -1971,11 +1971,11 @@
       </c>
       <c r="I11">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K11">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L11">
         <f t="shared" ca="1" si="2"/>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="D12">
         <f t="shared" ca="1" si="0"/>
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -2004,15 +2004,15 @@
       </c>
       <c r="I12">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K12">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L12">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="D13">
         <f t="shared" ca="1" si="0"/>
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="E13">
         <v>2</v>
@@ -2041,11 +2041,11 @@
       </c>
       <c r="K13">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L13">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -2060,7 +2060,7 @@
       </c>
       <c r="D14">
         <f t="shared" ca="1" si="0"/>
-        <v>40</v>
+        <v>116</v>
       </c>
       <c r="E14">
         <v>2</v>
@@ -2070,15 +2070,15 @@
       </c>
       <c r="I14">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K14">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L14">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="D15">
         <f t="shared" ca="1" si="0"/>
-        <v>89</v>
+        <v>52</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -2103,11 +2103,11 @@
       </c>
       <c r="I15">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K15">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L15">
         <f t="shared" ca="1" si="2"/>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="D16">
         <f t="shared" ca="1" si="0"/>
-        <v>11</v>
+        <v>80</v>
       </c>
       <c r="E16">
         <v>3</v>
@@ -2136,15 +2136,15 @@
       </c>
       <c r="I16">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K16">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L16">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:24">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="D17">
         <f t="shared" ca="1" si="0"/>
-        <v>40</v>
+        <v>118</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -2169,11 +2169,11 @@
       </c>
       <c r="I17">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K17">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L17">
         <f t="shared" ca="1" si="2"/>
@@ -2192,7 +2192,7 @@
       </c>
       <c r="D18">
         <f t="shared" ca="1" si="0"/>
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="E18">
         <v>2</v>
@@ -2202,11 +2202,11 @@
       </c>
       <c r="I18">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K18">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L18">
         <f t="shared" ca="1" si="2"/>
@@ -2225,7 +2225,7 @@
       </c>
       <c r="D19">
         <f t="shared" ca="1" si="0"/>
-        <v>34</v>
+        <v>91</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -2235,11 +2235,11 @@
       </c>
       <c r="I19">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K19">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L19">
         <f t="shared" ca="1" si="2"/>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="D20">
         <f t="shared" ca="1" si="0"/>
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="E20">
         <v>2</v>
@@ -2268,15 +2268,15 @@
       </c>
       <c r="I20">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K20">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L20">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:24">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="D21">
         <f t="shared" ca="1" si="0"/>
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -2301,15 +2301,15 @@
       </c>
       <c r="I21">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K21">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L21">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:24">
@@ -2454,7 +2454,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E3CF6DF-5DC6-4F82-AD2C-07BC625FD2D9}">
   <dimension ref="A1:G8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col min="5" max="5" width="19.6640625" bestFit="1" customWidth="1"/>
   </cols>

--- a/inputData/inputData.xlsx
+++ b/inputData/inputData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kapta\Documents\DTU\Speciale\GitHubFiles\inputData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/inputData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB02FBFD-7CAE-452B-90DF-6CB665492C2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09258F7E-AE3E-0F42-8159-2876CA79017F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16340" activeTab="2" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="PlaneData" sheetId="7" r:id="rId1"/>
@@ -545,7 +545,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A94FE46B-0EE8-4D7E-956E-06AD6DDE4FF5}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
@@ -598,7 +598,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{332D5C3C-A1DF-48A5-A3F8-29AFDB8C103D}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -607,7 +607,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64A48C4B-C23A-0343-9CD4-B20C0FE9227B}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
@@ -652,7 +652,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3245F359-CA05-2247-86C6-92433A84B0A2}">
   <dimension ref="A1:F20"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col min="3" max="3" width="22.5" customWidth="1"/>
     <col min="4" max="4" width="13.33203125" bestFit="1" customWidth="1"/>
@@ -773,7 +773,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0891C305-141D-384C-BB9E-30507F3FCDCC}">
   <dimension ref="A1:X32"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col min="5" max="5" width="11.83203125" customWidth="1"/>
     <col min="6" max="6" width="11.5" customWidth="1"/>
@@ -1341,7 +1341,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF01B7F4-A8F2-E74F-93E1-1ACB4B99B891}">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
@@ -1411,7 +1411,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4154E97-9715-C248-8300-688A466787B4}">
   <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col min="3" max="3" width="12.5" customWidth="1"/>
   </cols>
@@ -1490,7 +1490,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30A04F2A-161E-4502-9547-1DD0A31CBA64}">
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col min="3" max="3" width="12.5" customWidth="1"/>
     <col min="4" max="4" width="17.5" bestFit="1" customWidth="1"/>
@@ -1623,7 +1623,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A73ABDEA-DD83-4C31-B1A2-B93032C8B1F1}">
   <dimension ref="A1:X32"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col min="5" max="5" width="11.83203125" customWidth="1"/>
     <col min="6" max="6" width="11.5" customWidth="1"/>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="D2">
         <f ca="1">RANDBETWEEN(10,120)</f>
-        <v>114</v>
+        <v>20</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="I2">
         <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K2">
         <f ca="1">RANDBETWEEN(1,5)</f>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L2">
         <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="D3">
         <f t="shared" ref="D3:D21" ca="1" si="0">RANDBETWEEN(10,120)</f>
-        <v>72</v>
+        <v>106</v>
       </c>
       <c r="E3">
         <v>3</v>
@@ -1707,15 +1707,15 @@
       </c>
       <c r="I3">
         <f t="shared" ref="I3:I21" ca="1" si="1">RANDBETWEEN(1,5)</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K3">
         <f t="shared" ref="K3:L21" ca="1" si="2">RANDBETWEEN(1,5)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L3">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="D4">
         <f t="shared" ca="1" si="0"/>
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -1740,15 +1740,15 @@
       </c>
       <c r="I4">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K4">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L4">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="D5">
         <f t="shared" ca="1" si="0"/>
-        <v>72</v>
+        <v>110</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -1773,15 +1773,15 @@
       </c>
       <c r="I5">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K5">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L5">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="D6">
         <f t="shared" ca="1" si="0"/>
-        <v>76</v>
+        <v>17</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1806,15 +1806,15 @@
       </c>
       <c r="I6">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K6">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L6">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="D7">
         <f t="shared" ca="1" si="0"/>
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -1839,11 +1839,11 @@
       </c>
       <c r="I7">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K7">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L7">
         <f t="shared" ca="1" si="2"/>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="D8">
         <f t="shared" ca="1" si="0"/>
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="L8">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="D9">
         <f t="shared" ca="1" si="0"/>
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="E9">
         <v>2</v>
@@ -1905,15 +1905,15 @@
       </c>
       <c r="I9">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K9">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L9">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="D10">
         <f t="shared" ca="1" si="0"/>
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -1938,15 +1938,15 @@
       </c>
       <c r="I10">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K10">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L10">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="D11">
         <f t="shared" ca="1" si="0"/>
-        <v>62</v>
+        <v>111</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -1971,11 +1971,11 @@
       </c>
       <c r="I11">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K11">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L11">
         <f t="shared" ca="1" si="2"/>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="D12">
         <f t="shared" ca="1" si="0"/>
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -2004,15 +2004,15 @@
       </c>
       <c r="I12">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K12">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L12">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="D13">
         <f t="shared" ca="1" si="0"/>
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="E13">
         <v>2</v>
@@ -2041,11 +2041,11 @@
       </c>
       <c r="K13">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L13">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -2060,7 +2060,7 @@
       </c>
       <c r="D14">
         <f t="shared" ca="1" si="0"/>
-        <v>116</v>
+        <v>40</v>
       </c>
       <c r="E14">
         <v>2</v>
@@ -2070,15 +2070,15 @@
       </c>
       <c r="I14">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K14">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L14">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="D15">
         <f t="shared" ca="1" si="0"/>
-        <v>52</v>
+        <v>89</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -2103,11 +2103,11 @@
       </c>
       <c r="I15">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K15">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L15">
         <f t="shared" ca="1" si="2"/>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="D16">
         <f t="shared" ca="1" si="0"/>
-        <v>80</v>
+        <v>11</v>
       </c>
       <c r="E16">
         <v>3</v>
@@ -2136,15 +2136,15 @@
       </c>
       <c r="I16">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K16">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L16">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:24">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="D17">
         <f t="shared" ca="1" si="0"/>
-        <v>118</v>
+        <v>40</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -2169,11 +2169,11 @@
       </c>
       <c r="I17">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K17">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L17">
         <f t="shared" ca="1" si="2"/>
@@ -2192,7 +2192,7 @@
       </c>
       <c r="D18">
         <f t="shared" ca="1" si="0"/>
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="E18">
         <v>2</v>
@@ -2202,11 +2202,11 @@
       </c>
       <c r="I18">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K18">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L18">
         <f t="shared" ca="1" si="2"/>
@@ -2225,7 +2225,7 @@
       </c>
       <c r="D19">
         <f t="shared" ca="1" si="0"/>
-        <v>91</v>
+        <v>34</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -2235,11 +2235,11 @@
       </c>
       <c r="I19">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K19">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L19">
         <f t="shared" ca="1" si="2"/>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="D20">
         <f t="shared" ca="1" si="0"/>
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="E20">
         <v>2</v>
@@ -2268,15 +2268,15 @@
       </c>
       <c r="I20">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K20">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L20">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:24">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="D21">
         <f t="shared" ca="1" si="0"/>
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -2301,15 +2301,15 @@
       </c>
       <c r="I21">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K21">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L21">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:24">
@@ -2454,7 +2454,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E3CF6DF-5DC6-4F82-AD2C-07BC625FD2D9}">
   <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col min="5" max="5" width="19.6640625" bestFit="1" customWidth="1"/>
   </cols>
